--- a/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Bundle-OP-Accept.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Bundle-OP-Accept.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4070" uniqueCount="348">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4090" uniqueCount="358">
   <si>
     <t>Property</t>
   </si>
@@ -265,8 +265,8 @@
     <t>A container for a collection of resources.</t>
   </si>
   <si>
-    <t>bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}
-bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}</t>
+    <t>bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}
+bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}</t>
   </si>
   <si>
     <t>N/A</t>
@@ -381,6 +381,16 @@
   </si>
   <si>
     <t>Persistent identity generally only matters for batches of type Document, Message, and Collection. It would not normally be populated for search and history results and servers ignore Bundle.identifier when processing batches and transactions. For Documents  the .identifier SHALL be populated such that the .identifier is globally unique.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
+    <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
+  </si>
+  <si>
+    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
   </si>
   <si>
     <t>ClinicalDocument.id</t>
@@ -483,6 +493,9 @@
 This specification defines some specific uses of Bundle.link for [searching](http://hl7.org/fhir/R4/search.html#conformance) and [paging](http://hl7.org/fhir/R4/http.html#paging), but no specific uses for Bundle.entry.link, and no defined function in a transaction - the meaning is implementation specific.</t>
   </si>
   <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>Bundle.link.id</t>
   </si>
   <si>
@@ -499,9 +512,6 @@
     <t>Element.id</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Bundle.link.extension</t>
   </si>
   <si>
@@ -522,6 +532,16 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
     <t>Element.extension</t>
   </si>
   <si>
@@ -558,6 +578,9 @@
     <t>A name which details the functional use for this link - see [http://www.iana.org/assignments/link-relations/link-relations.xhtml#link-relations-1](http://www.iana.org/assignments/link-relations/link-relations.xhtml#link-relations-1).</t>
   </si>
   <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
+  </si>
+  <si>
     <t>Bundle.link.url</t>
   </si>
   <si>
@@ -565,6 +588,9 @@
   </si>
   <si>
     <t>The reference details for the link.</t>
+  </si>
+  <si>
+    <t>see http://en.wikipedia.org/wiki/Uniform_resource_identifier</t>
   </si>
   <si>
     <t>Bundle.entry</t>
@@ -589,8 +615,8 @@
     <t>closed</t>
   </si>
   <si>
-    <t>bdl-5:must be a resource unless there's a request or response {resource.exists() or request.exists() or response.exists()}
-bdl-8:fullUrl cannot be a version specific reference {fullUrl.contains('/_history/').not()}ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+bdl-8:fullUrl cannot be a version specific reference {fullUrl.contains('/_history/').not()}bdl-5:must be a resource unless there's a request or response {resource.exists() or request.exists() or response.exists()}</t>
   </si>
   <si>
     <t>Bundle.entry.id</t>
@@ -639,6 +665,9 @@
     <t>The Resource for the entry. The purpose/meaning of the resource is determined by the Bundle.type.</t>
   </si>
   <si>
+    <t>Entity. Role, or Act</t>
+  </si>
+  <si>
     <t>Bundle.entry.search</t>
   </si>
   <si>
@@ -648,8 +677,8 @@
     <t>Information about the search process that lead to the creation of this entry.</t>
   </si>
   <si>
-    <t xml:space="preserve">bdl-2
-</t>
+    <t>ele-1
+bdl-2</t>
   </si>
   <si>
     <t>Bundle.entry.search.id</t>
@@ -705,8 +734,8 @@
     <t>Additional information about how this entry should be processed as part of a transaction or batch.  For history, it shows how the entry was processed to create the version contained in the entry.</t>
   </si>
   <si>
-    <t xml:space="preserve">bdl-3
-</t>
+    <t>ele-1
+bdl-3</t>
   </si>
   <si>
     <t>Bundle.entry.request.id</t>
@@ -760,6 +789,9 @@
     <t>Only perform the operation if the last updated date matches. See the API documentation for ["Conditional Read"](http://hl7.org/fhir/R4/http.html#cread).</t>
   </si>
   <si>
+    <t>Note: This is intended for where precisely observed times are required, typically system logs etc., and not human-reported times - for them, see date and dateTime (which can be as precise as instant, but is not required to be) below. Time zone is always required</t>
+  </si>
+  <si>
     <t>Bundle.entry.request.ifMatch</t>
   </si>
   <si>
@@ -787,8 +819,8 @@
     <t>Indicates the results of processing the corresponding 'request' entry in the batch or transaction being responded to or what the results of an operation where when returning history.</t>
   </si>
   <si>
-    <t xml:space="preserve">bdl-4
-</t>
+    <t>ele-1
+bdl-4</t>
   </si>
   <si>
     <t>Bundle.entry.response.id</t>
@@ -1434,15 +1466,15 @@
     <col min="26" max="26" width="42.01953125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="34.91015625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.98828125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="24.1328125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="22.78515625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="53.91015625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="123.23828125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="36.84375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
@@ -2231,30 +2263,30 @@
         <v>87</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="AJ7" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>77</v>
+        <v>121</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>77</v>
+        <v>122</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="AN7" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2280,13 +2312,13 @@
         <v>107</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2294,7 +2326,7 @@
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="S8" t="s" s="2">
         <v>77</v>
@@ -2312,13 +2344,13 @@
         <v>77</v>
       </c>
       <c r="X8" t="s" s="2">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="Y8" t="s" s="2">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="Z8" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="AA8" t="s" s="2">
         <v>77</v>
@@ -2336,7 +2368,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>87</v>
@@ -2360,15 +2392,15 @@
         <v>77</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2391,16 +2423,16 @@
         <v>88</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2450,7 +2482,7 @@
         <v>77</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2471,18 +2503,18 @@
         <v>77</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2505,16 +2537,16 @@
         <v>88</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2564,7 +2596,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2573,7 +2605,7 @@
         <v>87</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>99</v>
@@ -2593,10 +2625,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2619,16 +2651,16 @@
         <v>88</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2678,7 +2710,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2687,7 +2719,7 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>99</v>
@@ -2696,7 +2728,7 @@
         <v>77</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>77</v>
@@ -2707,10 +2739,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2733,13 +2765,13 @@
         <v>77</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2790,7 +2822,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2808,7 +2840,7 @@
         <v>77</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>77</v>
@@ -2819,14 +2851,14 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -2845,16 +2877,16 @@
         <v>77</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2892,19 +2924,19 @@
         <v>77</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -2916,13 +2948,13 @@
         <v>77</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>77</v>
@@ -2933,14 +2965,14 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -2959,19 +2991,19 @@
         <v>88</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>77</v>
@@ -3020,7 +3052,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3032,7 +3064,7 @@
         <v>77</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>77</v>
@@ -3049,10 +3081,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3075,15 +3107,17 @@
         <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N15" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>77</v>
@@ -3132,7 +3166,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>87</v>
@@ -3161,10 +3195,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3190,12 +3224,14 @@
         <v>101</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N16" s="2"/>
+        <v>181</v>
+      </c>
+      <c r="N16" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3244,7 +3280,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>87</v>
@@ -3273,10 +3309,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3284,10 +3320,10 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>77</v>
@@ -3299,13 +3335,13 @@
         <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3344,19 +3380,19 @@
         <v>77</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3365,16 +3401,16 @@
         <v>79</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>77</v>
@@ -3385,10 +3421,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3411,13 +3447,13 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3468,7 +3504,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3486,7 +3522,7 @@
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -3497,14 +3533,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3523,16 +3559,16 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3570,19 +3606,19 @@
         <v>77</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3594,13 +3630,13 @@
         <v>77</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -3611,14 +3647,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3637,19 +3673,19 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>77</v>
@@ -3698,7 +3734,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3710,7 +3746,7 @@
         <v>77</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>77</v>
@@ -3727,10 +3763,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3756,10 +3792,10 @@
         <v>77</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3810,7 +3846,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3822,7 +3858,7 @@
         <v>77</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>77</v>
@@ -3839,10 +3875,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3868,13 +3904,13 @@
         <v>101</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3924,7 +3960,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3953,10 +3989,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3979,13 +4015,13 @@
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4036,7 +4072,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4054,7 +4090,7 @@
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>77</v>
+        <v>205</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
@@ -4065,10 +4101,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4091,13 +4127,13 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4148,7 +4184,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4157,7 +4193,7 @@
         <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>99</v>
@@ -4166,7 +4202,7 @@
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
@@ -4177,10 +4213,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4203,13 +4239,13 @@
         <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4260,7 +4296,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4278,7 +4314,7 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -4289,14 +4325,14 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4315,16 +4351,16 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4362,19 +4398,19 @@
         <v>77</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4386,13 +4422,13 @@
         <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4403,14 +4439,14 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4429,19 +4465,19 @@
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4490,7 +4526,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4502,7 +4538,7 @@
         <v>77</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>77</v>
@@ -4519,10 +4555,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4548,13 +4584,13 @@
         <v>107</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4580,13 +4616,13 @@
         <v>77</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>77</v>
@@ -4604,7 +4640,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4633,10 +4669,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4659,16 +4695,16 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4718,7 +4754,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4727,7 +4763,7 @@
         <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>99</v>
@@ -4736,7 +4772,7 @@
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
@@ -4747,10 +4783,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4773,13 +4809,13 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4830,7 +4866,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4839,7 +4875,7 @@
         <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>99</v>
@@ -4848,7 +4884,7 @@
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
@@ -4859,10 +4895,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4885,13 +4921,13 @@
         <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4942,7 +4978,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -4960,7 +4996,7 @@
         <v>77</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>77</v>
@@ -4971,14 +5007,14 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -4997,16 +5033,16 @@
         <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5044,19 +5080,19 @@
         <v>77</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5068,13 +5104,13 @@
         <v>77</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
@@ -5085,14 +5121,14 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5111,19 +5147,19 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5172,7 +5208,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5184,7 +5220,7 @@
         <v>77</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>77</v>
@@ -5201,10 +5237,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5230,10 +5266,10 @@
         <v>107</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5260,13 +5296,13 @@
         <v>77</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>77</v>
@@ -5284,7 +5320,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>87</v>
@@ -5313,10 +5349,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5342,13 +5378,13 @@
         <v>101</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5398,7 +5434,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>87</v>
@@ -5427,10 +5463,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5453,15 +5489,17 @@
         <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N36" s="2"/>
+        <v>242</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5510,7 +5548,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5539,10 +5577,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5565,15 +5603,17 @@
         <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -5622,7 +5662,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5651,10 +5691,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5677,15 +5717,17 @@
         <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -5734,7 +5776,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5763,10 +5805,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5789,15 +5831,17 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -5846,7 +5890,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5875,10 +5919,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5901,13 +5945,13 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5958,7 +6002,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -5967,7 +6011,7 @@
         <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>99</v>
@@ -5976,7 +6020,7 @@
         <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
@@ -5987,10 +6031,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6013,13 +6057,13 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6070,7 +6114,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6088,7 +6132,7 @@
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -6099,14 +6143,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6125,16 +6169,16 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6172,19 +6216,19 @@
         <v>77</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6196,13 +6240,13 @@
         <v>77</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -6213,14 +6257,14 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6239,19 +6283,19 @@
         <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -6300,7 +6344,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6312,7 +6356,7 @@
         <v>77</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>77</v>
@@ -6329,10 +6373,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6355,15 +6399,17 @@
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -6412,7 +6458,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>87</v>
@@ -6441,10 +6487,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6470,12 +6516,14 @@
         <v>101</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6524,7 +6572,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6553,10 +6601,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6579,16 +6627,16 @@
         <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6638,7 +6686,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6667,10 +6715,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6693,16 +6741,16 @@
         <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6752,7 +6800,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6781,10 +6829,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6807,16 +6855,16 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6866,7 +6914,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -6884,7 +6932,7 @@
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>77</v>
+        <v>205</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>
@@ -6895,13 +6943,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>77</v>
@@ -6923,13 +6971,13 @@
         <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6980,7 +7028,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -6989,16 +7037,16 @@
         <v>79</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
@@ -7009,10 +7057,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7035,13 +7083,13 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7092,7 +7140,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7110,7 +7158,7 @@
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>77</v>
@@ -7121,14 +7169,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7147,16 +7195,16 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7194,19 +7242,19 @@
         <v>77</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7218,13 +7266,13 @@
         <v>77</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
@@ -7235,14 +7283,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7261,19 +7309,19 @@
         <v>88</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -7322,7 +7370,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7334,7 +7382,7 @@
         <v>77</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>77</v>
@@ -7351,10 +7399,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7380,10 +7428,10 @@
         <v>80</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7434,7 +7482,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7446,7 +7494,7 @@
         <v>77</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>77</v>
@@ -7463,10 +7511,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7492,13 +7540,13 @@
         <v>101</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7548,7 +7596,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7577,10 +7625,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7603,13 +7651,13 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7660,7 +7708,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7678,7 +7726,7 @@
         <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
@@ -7689,10 +7737,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7715,13 +7763,13 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7772,7 +7820,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -7781,7 +7829,7 @@
         <v>87</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>99</v>
@@ -7790,7 +7838,7 @@
         <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
@@ -7801,10 +7849,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7827,13 +7875,13 @@
         <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7884,7 +7932,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -7902,7 +7950,7 @@
         <v>77</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>77</v>
@@ -7913,14 +7961,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -7939,16 +7987,16 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -7986,19 +8034,19 @@
         <v>77</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8010,13 +8058,13 @@
         <v>77</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>77</v>
@@ -8027,14 +8075,14 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8053,19 +8101,19 @@
         <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -8114,7 +8162,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8126,7 +8174,7 @@
         <v>77</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>77</v>
@@ -8143,10 +8191,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8172,13 +8220,13 @@
         <v>107</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8204,13 +8252,13 @@
         <v>77</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>77</v>
@@ -8228,7 +8276,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8257,10 +8305,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8283,16 +8331,16 @@
         <v>88</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8342,7 +8390,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8351,7 +8399,7 @@
         <v>87</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>99</v>
@@ -8360,7 +8408,7 @@
         <v>77</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>
@@ -8371,10 +8419,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8397,13 +8445,13 @@
         <v>88</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8454,7 +8502,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8463,7 +8511,7 @@
         <v>87</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>99</v>
@@ -8472,7 +8520,7 @@
         <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
@@ -8483,10 +8531,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8509,13 +8557,13 @@
         <v>77</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8566,7 +8614,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -8584,7 +8632,7 @@
         <v>77</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>77</v>
@@ -8595,14 +8643,14 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -8621,16 +8669,16 @@
         <v>77</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8668,19 +8716,19 @@
         <v>77</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -8692,13 +8740,13 @@
         <v>77</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>77</v>
@@ -8709,14 +8757,14 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -8735,19 +8783,19 @@
         <v>88</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>77</v>
@@ -8796,7 +8844,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -8808,7 +8856,7 @@
         <v>77</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>77</v>
@@ -8825,10 +8873,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8854,10 +8902,10 @@
         <v>107</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8884,13 +8932,13 @@
         <v>77</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>77</v>
@@ -8908,7 +8956,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>87</v>
@@ -8937,10 +8985,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8966,13 +9014,13 @@
         <v>101</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9022,7 +9070,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>87</v>
@@ -9051,10 +9099,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9077,15 +9125,17 @@
         <v>88</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N68" s="2"/>
+        <v>242</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>77</v>
@@ -9134,7 +9184,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9163,10 +9213,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9189,15 +9239,17 @@
         <v>88</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>77</v>
@@ -9246,7 +9298,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9275,10 +9327,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9301,15 +9353,17 @@
         <v>88</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>77</v>
@@ -9358,7 +9412,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -9387,10 +9441,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9413,15 +9467,17 @@
         <v>88</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N71" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>77</v>
@@ -9470,7 +9526,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -9499,10 +9555,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9525,13 +9581,13 @@
         <v>88</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -9582,7 +9638,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -9591,7 +9647,7 @@
         <v>87</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>99</v>
@@ -9600,7 +9656,7 @@
         <v>77</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>77</v>
@@ -9611,10 +9667,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9637,13 +9693,13 @@
         <v>77</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9694,7 +9750,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -9712,7 +9768,7 @@
         <v>77</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>77</v>
@@ -9723,14 +9779,14 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -9749,16 +9805,16 @@
         <v>77</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -9796,19 +9852,19 @@
         <v>77</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -9820,13 +9876,13 @@
         <v>77</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>77</v>
@@ -9837,14 +9893,14 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -9863,19 +9919,19 @@
         <v>88</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>77</v>
@@ -9924,7 +9980,7 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -9936,7 +9992,7 @@
         <v>77</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>77</v>
@@ -9953,10 +10009,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9979,15 +10035,17 @@
         <v>88</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N76" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>77</v>
@@ -10036,7 +10094,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>87</v>
@@ -10065,10 +10123,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10094,12 +10152,14 @@
         <v>101</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="N77" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>77</v>
@@ -10148,7 +10208,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -10177,10 +10237,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10203,16 +10263,16 @@
         <v>88</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -10262,7 +10322,7 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -10291,10 +10351,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10317,16 +10377,16 @@
         <v>88</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -10376,7 +10436,7 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -10405,10 +10465,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10431,16 +10491,16 @@
         <v>88</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -10490,7 +10550,7 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -10508,7 +10568,7 @@
         <v>77</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>77</v>
+        <v>205</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>77</v>
@@ -10519,13 +10579,13 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="D81" t="s" s="2">
         <v>77</v>
@@ -10547,13 +10607,13 @@
         <v>88</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -10604,7 +10664,7 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -10613,16 +10673,16 @@
         <v>79</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>77</v>
@@ -10633,10 +10693,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10659,13 +10719,13 @@
         <v>77</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -10716,7 +10776,7 @@
         <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -10734,7 +10794,7 @@
         <v>77</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>77</v>
@@ -10745,14 +10805,14 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -10771,16 +10831,16 @@
         <v>77</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -10818,19 +10878,19 @@
         <v>77</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC83" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -10842,13 +10902,13 @@
         <v>77</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>77</v>
@@ -10859,14 +10919,14 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -10885,19 +10945,19 @@
         <v>88</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>77</v>
@@ -10946,7 +11006,7 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -10958,7 +11018,7 @@
         <v>77</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>77</v>
@@ -10975,10 +11035,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11004,10 +11064,10 @@
         <v>80</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11058,7 +11118,7 @@
         <v>77</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -11070,7 +11130,7 @@
         <v>77</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>77</v>
@@ -11087,10 +11147,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11116,13 +11176,13 @@
         <v>101</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -11172,7 +11232,7 @@
         <v>77</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -11201,10 +11261,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11227,16 +11287,16 @@
         <v>77</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -11286,7 +11346,7 @@
         <v>77</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -11304,7 +11364,7 @@
         <v>77</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>77</v>
@@ -11315,10 +11375,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11341,13 +11401,13 @@
         <v>88</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -11398,7 +11458,7 @@
         <v>77</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -11407,7 +11467,7 @@
         <v>87</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>99</v>
@@ -11416,7 +11476,7 @@
         <v>77</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>77</v>
@@ -11427,10 +11487,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11453,13 +11513,13 @@
         <v>77</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -11510,7 +11570,7 @@
         <v>77</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -11528,7 +11588,7 @@
         <v>77</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>77</v>
@@ -11539,14 +11599,14 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -11565,16 +11625,16 @@
         <v>77</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -11612,19 +11672,19 @@
         <v>77</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC90" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD90" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -11636,13 +11696,13 @@
         <v>77</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>77</v>
@@ -11653,14 +11713,14 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -11679,19 +11739,19 @@
         <v>88</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>77</v>
@@ -11740,7 +11800,7 @@
         <v>77</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -11752,7 +11812,7 @@
         <v>77</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>77</v>
@@ -11769,10 +11829,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11798,13 +11858,13 @@
         <v>107</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -11830,13 +11890,13 @@
         <v>77</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>77</v>
@@ -11854,7 +11914,7 @@
         <v>77</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -11883,10 +11943,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11909,16 +11969,16 @@
         <v>88</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -11968,7 +12028,7 @@
         <v>77</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -11977,7 +12037,7 @@
         <v>87</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>99</v>
@@ -11986,7 +12046,7 @@
         <v>77</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>77</v>
@@ -11997,10 +12057,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12023,13 +12083,13 @@
         <v>88</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -12080,7 +12140,7 @@
         <v>77</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -12089,7 +12149,7 @@
         <v>87</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>99</v>
@@ -12098,7 +12158,7 @@
         <v>77</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>77</v>
@@ -12109,10 +12169,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12135,13 +12195,13 @@
         <v>77</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -12192,7 +12252,7 @@
         <v>77</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -12210,7 +12270,7 @@
         <v>77</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>77</v>
@@ -12221,14 +12281,14 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -12247,16 +12307,16 @@
         <v>77</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -12294,19 +12354,19 @@
         <v>77</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -12318,13 +12378,13 @@
         <v>77</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>77</v>
@@ -12335,14 +12395,14 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -12361,19 +12421,19 @@
         <v>88</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>77</v>
@@ -12422,7 +12482,7 @@
         <v>77</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -12434,7 +12494,7 @@
         <v>77</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>77</v>
@@ -12451,10 +12511,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12480,10 +12540,10 @@
         <v>107</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -12510,13 +12570,13 @@
         <v>77</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>77</v>
@@ -12534,7 +12594,7 @@
         <v>77</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>87</v>
@@ -12563,10 +12623,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12592,13 +12652,13 @@
         <v>101</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -12648,7 +12708,7 @@
         <v>77</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>87</v>
@@ -12677,10 +12737,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12703,15 +12763,17 @@
         <v>88</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N100" s="2"/>
+        <v>242</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>77</v>
@@ -12760,7 +12822,7 @@
         <v>77</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -12789,10 +12851,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12815,15 +12877,17 @@
         <v>88</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N101" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="N101" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>77</v>
@@ -12872,7 +12936,7 @@
         <v>77</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -12901,10 +12965,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12927,15 +12991,17 @@
         <v>88</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N102" s="2"/>
+        <v>248</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>77</v>
@@ -12984,7 +13050,7 @@
         <v>77</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -13013,10 +13079,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13039,15 +13105,17 @@
         <v>88</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N103" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>77</v>
@@ -13096,7 +13164,7 @@
         <v>77</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -13125,10 +13193,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13151,13 +13219,13 @@
         <v>88</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -13208,7 +13276,7 @@
         <v>77</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -13217,7 +13285,7 @@
         <v>87</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>99</v>
@@ -13226,7 +13294,7 @@
         <v>77</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>77</v>
@@ -13237,10 +13305,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13263,13 +13331,13 @@
         <v>77</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -13320,7 +13388,7 @@
         <v>77</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -13338,7 +13406,7 @@
         <v>77</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>77</v>
@@ -13349,14 +13417,14 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -13375,16 +13443,16 @@
         <v>77</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -13422,19 +13490,19 @@
         <v>77</v>
       </c>
       <c r="AB106" t="s" s="2">
-        <v>77</v>
+        <v>164</v>
       </c>
       <c r="AC106" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AD106" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -13446,13 +13514,13 @@
         <v>77</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>77</v>
@@ -13463,14 +13531,14 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
@@ -13489,19 +13557,19 @@
         <v>88</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="O107" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>77</v>
@@ -13550,7 +13618,7 @@
         <v>77</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -13562,7 +13630,7 @@
         <v>77</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>77</v>
@@ -13579,10 +13647,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13605,15 +13673,17 @@
         <v>88</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N108" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>77</v>
@@ -13662,7 +13732,7 @@
         <v>77</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>87</v>
@@ -13691,10 +13761,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13720,12 +13790,14 @@
         <v>101</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="N109" s="2"/>
+        <v>264</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>182</v>
+      </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>77</v>
@@ -13774,7 +13846,7 @@
         <v>77</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -13803,10 +13875,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13829,16 +13901,16 @@
         <v>88</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -13888,7 +13960,7 @@
         <v>77</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -13917,10 +13989,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13943,16 +14015,16 @@
         <v>88</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -14002,7 +14074,7 @@
         <v>77</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -14031,10 +14103,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14057,16 +14129,16 @@
         <v>88</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -14116,7 +14188,7 @@
         <v>77</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -14134,7 +14206,7 @@
         <v>77</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>77</v>
+        <v>205</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>77</v>
@@ -14145,10 +14217,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14171,19 +14243,19 @@
         <v>88</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>77</v>
@@ -14232,7 +14304,7 @@
         <v>77</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
@@ -14241,7 +14313,7 @@
         <v>87</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>99</v>
@@ -14250,7 +14322,7 @@
         <v>77</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>77</v>

--- a/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Bundle-OP-Accept.xlsx
+++ b/tiflow-core/develop/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Bundle-OP-Accept.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4090" uniqueCount="358">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4070" uniqueCount="348">
   <si>
     <t>Property</t>
   </si>
@@ -265,8 +265,8 @@
     <t>A container for a collection of resources.</t>
   </si>
   <si>
-    <t>bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}
-bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}</t>
+    <t>bdl-1:total only when a search or history {total.empty() or (type = 'searchset') or (type = 'history')}
+bdl-2:entry.search only when a search {entry.search.empty() or (type = 'searchset')}bdl-3:entry.request mandatory for batch/transaction/history, otherwise prohibited {entry.all(request.exists() = (%resource.type = 'batch' or %resource.type = 'transaction' or %resource.type = 'history'))}bdl-4:entry.response mandatory for batch-response/transaction-response/history, otherwise prohibited {entry.all(response.exists() = (%resource.type = 'batch-response' or %resource.type = 'transaction-response' or %resource.type = 'history'))}bdl-7:FullUrl must be unique in a bundle, or else entries with the same fullUrl must have different meta.versionId (except in history bundles) {(type = 'history') or entry.where(fullUrl.exists()).select(fullUrl&amp;resource.meta.versionId).isDistinct()}bdl-9:A document must have an identifier with a system and a value {type = 'document' implies (identifier.system.exists() and identifier.value.exists())}bdl-10:A document must have a date {type = 'document' implies (timestamp.hasValue())}bdl-11:A document must have a Composition as the first resource {type = 'document' implies entry.first().resource.is(Composition)}bdl-12:A message must have a MessageHeader as the first resource {type = 'message' implies entry.first().resource.is(MessageHeader)}</t>
   </si>
   <si>
     <t>N/A</t>
@@ -381,16 +381,6 @@
   </si>
   <si>
     <t>Persistent identity generally only matters for batches of type Document, Message, and Collection. It would not normally be populated for search and history results and servers ignore Bundle.identifier when processing batches and transactions. For Documents  the .identifier SHALL be populated such that the .identifier is globally unique.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
-  </si>
-  <si>
-    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
   </si>
   <si>
     <t>ClinicalDocument.id</t>
@@ -493,9 +483,6 @@
 This specification defines some specific uses of Bundle.link for [searching](http://hl7.org/fhir/R4/search.html#conformance) and [paging](http://hl7.org/fhir/R4/http.html#paging), but no specific uses for Bundle.entry.link, and no defined function in a transaction - the meaning is implementation specific.</t>
   </si>
   <si>
-    <t>n/a</t>
-  </si>
-  <si>
     <t>Bundle.link.id</t>
   </si>
   <si>
@@ -512,6 +499,9 @@
     <t>Element.id</t>
   </si>
   <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>Bundle.link.extension</t>
   </si>
   <si>
@@ -532,16 +522,6 @@
     <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>Element.extension</t>
   </si>
   <si>
@@ -578,9 +558,6 @@
     <t>A name which details the functional use for this link - see [http://www.iana.org/assignments/link-relations/link-relations.xhtml#link-relations-1](http://www.iana.org/assignments/link-relations/link-relations.xhtml#link-relations-1).</t>
   </si>
   <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
-  </si>
-  <si>
     <t>Bundle.link.url</t>
   </si>
   <si>
@@ -588,9 +565,6 @@
   </si>
   <si>
     <t>The reference details for the link.</t>
-  </si>
-  <si>
-    <t>see http://en.wikipedia.org/wiki/Uniform_resource_identifier</t>
   </si>
   <si>
     <t>Bundle.entry</t>
@@ -615,8 +589,8 @@
     <t>closed</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-bdl-8:fullUrl cannot be a version specific reference {fullUrl.contains('/_history/').not()}bdl-5:must be a resource unless there's a request or response {resource.exists() or request.exists() or response.exists()}</t>
+    <t>bdl-5:must be a resource unless there's a request or response {resource.exists() or request.exists() or response.exists()}
+bdl-8:fullUrl cannot be a version specific reference {fullUrl.contains('/_history/').not()}ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
   </si>
   <si>
     <t>Bundle.entry.id</t>
@@ -665,9 +639,6 @@
     <t>The Resource for the entry. The purpose/meaning of the resource is determined by the Bundle.type.</t>
   </si>
   <si>
-    <t>Entity. Role, or Act</t>
-  </si>
-  <si>
     <t>Bundle.entry.search</t>
   </si>
   <si>
@@ -677,8 +648,8 @@
     <t>Information about the search process that lead to the creation of this entry.</t>
   </si>
   <si>
-    <t>ele-1
-bdl-2</t>
+    <t xml:space="preserve">bdl-2
+</t>
   </si>
   <si>
     <t>Bundle.entry.search.id</t>
@@ -734,8 +705,8 @@
     <t>Additional information about how this entry should be processed as part of a transaction or batch.  For history, it shows how the entry was processed to create the version contained in the entry.</t>
   </si>
   <si>
-    <t>ele-1
-bdl-3</t>
+    <t xml:space="preserve">bdl-3
+</t>
   </si>
   <si>
     <t>Bundle.entry.request.id</t>
@@ -789,9 +760,6 @@
     <t>Only perform the operation if the last updated date matches. See the API documentation for ["Conditional Read"](http://hl7.org/fhir/R4/http.html#cread).</t>
   </si>
   <si>
-    <t>Note: This is intended for where precisely observed times are required, typically system logs etc., and not human-reported times - for them, see date and dateTime (which can be as precise as instant, but is not required to be) below. Time zone is always required</t>
-  </si>
-  <si>
     <t>Bundle.entry.request.ifMatch</t>
   </si>
   <si>
@@ -819,8 +787,8 @@
     <t>Indicates the results of processing the corresponding 'request' entry in the batch or transaction being responded to or what the results of an operation where when returning history.</t>
   </si>
   <si>
-    <t>ele-1
-bdl-4</t>
+    <t xml:space="preserve">bdl-4
+</t>
   </si>
   <si>
     <t>Bundle.entry.response.id</t>
@@ -1466,15 +1434,15 @@
     <col min="26" max="26" width="42.01953125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="34.91015625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="29.98828125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="53.91015625" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="123.23828125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="24.1328125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="22.78515625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="36.84375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
@@ -2263,30 +2231,30 @@
         <v>87</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>120</v>
+        <v>77</v>
       </c>
       <c r="AJ7" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM7" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AN7" t="s" s="2">
         <v>121</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>122</v>
-      </c>
-      <c r="AM7" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="AN7" t="s" s="2">
-        <v>124</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2312,13 +2280,13 @@
         <v>107</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2326,32 +2294,32 @@
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="S8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X8" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="Y8" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="Z8" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="S8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X8" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="Y8" t="s" s="2">
-        <v>131</v>
-      </c>
-      <c r="Z8" t="s" s="2">
-        <v>132</v>
-      </c>
       <c r="AA8" t="s" s="2">
         <v>77</v>
       </c>
@@ -2368,7 +2336,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>87</v>
@@ -2392,15 +2360,15 @@
         <v>77</v>
       </c>
       <c r="AN8" t="s" s="2">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2423,16 +2391,16 @@
         <v>88</v>
       </c>
       <c r="K9" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="M9" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="N9" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="L9" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="M9" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>138</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2482,7 +2450,7 @@
         <v>77</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2503,18 +2471,18 @@
         <v>77</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="AN9" t="s" s="2">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2537,16 +2505,16 @@
         <v>88</v>
       </c>
       <c r="K10" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M10" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="N10" t="s" s="2">
         <v>142</v>
-      </c>
-      <c r="L10" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="N10" t="s" s="2">
-        <v>145</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2596,7 +2564,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -2605,7 +2573,7 @@
         <v>87</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>99</v>
@@ -2625,10 +2593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2651,16 +2619,16 @@
         <v>88</v>
       </c>
       <c r="K11" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="L11" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="M11" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="N11" t="s" s="2">
         <v>148</v>
-      </c>
-      <c r="L11" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2710,7 +2678,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2719,7 +2687,7 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>120</v>
+        <v>77</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>99</v>
@@ -2728,7 +2696,7 @@
         <v>77</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>77</v>
@@ -2739,10 +2707,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2765,13 +2733,13 @@
         <v>77</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2822,7 +2790,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2840,7 +2808,7 @@
         <v>77</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>77</v>
@@ -2851,14 +2819,14 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
@@ -2877,16 +2845,16 @@
         <v>77</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N13" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L13" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -2924,19 +2892,19 @@
         <v>77</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -2948,13 +2916,13 @@
         <v>77</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>77</v>
@@ -2965,14 +2933,14 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -2991,19 +2959,19 @@
         <v>88</v>
       </c>
       <c r="K14" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L14" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L14" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O14" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>77</v>
@@ -3052,7 +3020,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3064,7 +3032,7 @@
         <v>77</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>77</v>
@@ -3081,10 +3049,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3107,17 +3075,15 @@
         <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>77</v>
@@ -3166,7 +3132,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>87</v>
@@ -3195,10 +3161,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3224,14 +3190,12 @@
         <v>101</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>182</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3280,7 +3244,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>87</v>
@@ -3309,10 +3273,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3320,10 +3284,10 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>77</v>
@@ -3335,13 +3299,13 @@
         <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3380,19 +3344,19 @@
         <v>77</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3401,16 +3365,16 @@
         <v>79</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>120</v>
+        <v>77</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>77</v>
@@ -3421,10 +3385,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3447,13 +3411,13 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3504,7 +3468,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3522,7 +3486,7 @@
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -3533,14 +3497,14 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3559,16 +3523,16 @@
         <v>77</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N19" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L19" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3606,19 +3570,19 @@
         <v>77</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3630,13 +3594,13 @@
         <v>77</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -3647,14 +3611,14 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3673,19 +3637,19 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M20" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N20" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L20" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O20" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>77</v>
@@ -3734,7 +3698,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3746,7 +3710,7 @@
         <v>77</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>77</v>
@@ -3763,10 +3727,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3792,10 +3756,10 @@
         <v>77</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3846,7 +3810,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3858,7 +3822,7 @@
         <v>77</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>77</v>
@@ -3875,10 +3839,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3904,13 +3868,13 @@
         <v>101</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -3960,7 +3924,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3989,10 +3953,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4015,13 +3979,13 @@
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4072,7 +4036,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4090,7 +4054,7 @@
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>205</v>
+        <v>77</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
@@ -4101,10 +4065,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4127,13 +4091,13 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4184,7 +4148,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4193,7 +4157,7 @@
         <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>99</v>
@@ -4202,7 +4166,7 @@
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
@@ -4213,10 +4177,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4239,13 +4203,13 @@
         <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4296,7 +4260,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4314,7 +4278,7 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -4325,14 +4289,14 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4351,16 +4315,16 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4398,19 +4362,19 @@
         <v>77</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4422,13 +4386,13 @@
         <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4439,14 +4403,14 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4465,19 +4429,19 @@
         <v>88</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L27" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O27" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>77</v>
@@ -4526,7 +4490,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4538,7 +4502,7 @@
         <v>77</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>77</v>
@@ -4555,10 +4519,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4584,13 +4548,13 @@
         <v>107</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4616,13 +4580,13 @@
         <v>77</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>77</v>
@@ -4640,7 +4604,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4669,10 +4633,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4695,16 +4659,16 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4754,7 +4718,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4763,7 +4727,7 @@
         <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>120</v>
+        <v>77</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>99</v>
@@ -4772,7 +4736,7 @@
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
@@ -4783,10 +4747,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4809,13 +4773,13 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4866,7 +4830,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4875,7 +4839,7 @@
         <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="AJ30" t="s" s="2">
         <v>99</v>
@@ -4884,7 +4848,7 @@
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
@@ -4895,10 +4859,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4921,13 +4885,13 @@
         <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4978,7 +4942,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -4996,7 +4960,7 @@
         <v>77</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>77</v>
@@ -5007,14 +4971,14 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5033,16 +4997,16 @@
         <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N32" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5080,19 +5044,19 @@
         <v>77</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5104,13 +5068,13 @@
         <v>77</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
@@ -5121,14 +5085,14 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5147,19 +5111,19 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N33" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L33" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M33" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O33" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5208,7 +5172,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5220,7 +5184,7 @@
         <v>77</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>77</v>
@@ -5237,10 +5201,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5266,10 +5230,10 @@
         <v>107</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5296,13 +5260,13 @@
         <v>77</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>77</v>
@@ -5320,7 +5284,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>87</v>
@@ -5349,10 +5313,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5378,13 +5342,13 @@
         <v>101</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5434,7 +5398,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>87</v>
@@ -5463,10 +5427,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5489,17 +5453,15 @@
         <v>88</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5548,7 +5510,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5577,10 +5539,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5603,17 +5565,15 @@
         <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -5662,7 +5622,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5691,10 +5651,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5717,17 +5677,15 @@
         <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -5776,7 +5734,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5805,10 +5763,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5831,17 +5789,15 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -5890,7 +5846,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5919,10 +5875,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5945,13 +5901,13 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6002,7 +5958,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6011,7 +5967,7 @@
         <v>87</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="AJ40" t="s" s="2">
         <v>99</v>
@@ -6020,7 +5976,7 @@
         <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
@@ -6031,10 +5987,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6057,13 +6013,13 @@
         <v>77</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6114,7 +6070,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6132,7 +6088,7 @@
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -6143,14 +6099,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6169,16 +6125,16 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L42" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6216,19 +6172,19 @@
         <v>77</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6240,13 +6196,13 @@
         <v>77</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -6257,14 +6213,14 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6283,19 +6239,19 @@
         <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N43" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L43" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O43" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -6344,7 +6300,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6356,7 +6312,7 @@
         <v>77</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>77</v>
@@ -6373,10 +6329,10 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6399,17 +6355,15 @@
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -6458,7 +6412,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>87</v>
@@ -6487,10 +6441,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6516,14 +6470,12 @@
         <v>101</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>182</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6572,7 +6524,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6601,10 +6553,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6627,16 +6579,16 @@
         <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6686,7 +6638,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6715,10 +6667,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6741,16 +6693,16 @@
         <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6800,7 +6752,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6829,10 +6781,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6855,16 +6807,16 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6914,7 +6866,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -6932,7 +6884,7 @@
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>205</v>
+        <v>77</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>
@@ -6943,13 +6895,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>77</v>
@@ -6971,13 +6923,13 @@
         <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7028,7 +6980,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7037,16 +6989,16 @@
         <v>79</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>120</v>
+        <v>77</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
@@ -7057,10 +7009,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7083,13 +7035,13 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7140,7 +7092,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7158,7 +7110,7 @@
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>77</v>
@@ -7169,14 +7121,14 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7195,16 +7147,16 @@
         <v>77</v>
       </c>
       <c r="K51" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7242,19 +7194,19 @@
         <v>77</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7266,13 +7218,13 @@
         <v>77</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
@@ -7283,14 +7235,14 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7309,19 +7261,19 @@
         <v>88</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N52" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L52" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O52" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -7370,7 +7322,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7382,7 +7334,7 @@
         <v>77</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>77</v>
@@ -7399,10 +7351,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7428,10 +7380,10 @@
         <v>80</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7482,7 +7434,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7494,7 +7446,7 @@
         <v>77</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>77</v>
@@ -7511,10 +7463,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7540,13 +7492,13 @@
         <v>101</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7596,7 +7548,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7625,10 +7577,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7651,13 +7603,13 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7708,7 +7660,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -7726,7 +7678,7 @@
         <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
@@ -7737,10 +7689,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7763,13 +7715,13 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7820,7 +7772,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -7829,7 +7781,7 @@
         <v>87</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>99</v>
@@ -7838,7 +7790,7 @@
         <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
@@ -7849,10 +7801,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7875,13 +7827,13 @@
         <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -7932,7 +7884,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -7950,7 +7902,7 @@
         <v>77</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>77</v>
@@ -7961,14 +7913,14 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -7987,16 +7939,16 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N58" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -8034,19 +7986,19 @@
         <v>77</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8058,13 +8010,13 @@
         <v>77</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>77</v>
@@ -8075,14 +8027,14 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8101,19 +8053,19 @@
         <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N59" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L59" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O59" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -8162,7 +8114,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8174,7 +8126,7 @@
         <v>77</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>77</v>
@@ -8191,10 +8143,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8220,13 +8172,13 @@
         <v>107</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8252,13 +8204,13 @@
         <v>77</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>77</v>
@@ -8276,7 +8228,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8305,10 +8257,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8331,16 +8283,16 @@
         <v>88</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8390,7 +8342,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8399,7 +8351,7 @@
         <v>87</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>120</v>
+        <v>77</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>99</v>
@@ -8408,7 +8360,7 @@
         <v>77</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>
@@ -8419,10 +8371,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8445,13 +8397,13 @@
         <v>88</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8502,7 +8454,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8511,7 +8463,7 @@
         <v>87</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>99</v>
@@ -8520,7 +8472,7 @@
         <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
@@ -8531,10 +8483,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8557,13 +8509,13 @@
         <v>77</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" s="2"/>
@@ -8614,7 +8566,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -8632,7 +8584,7 @@
         <v>77</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>77</v>
@@ -8643,14 +8595,14 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -8669,16 +8621,16 @@
         <v>77</v>
       </c>
       <c r="K64" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N64" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L64" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8716,19 +8668,19 @@
         <v>77</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC64" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -8740,13 +8692,13 @@
         <v>77</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>77</v>
@@ -8757,14 +8709,14 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
@@ -8783,19 +8735,19 @@
         <v>88</v>
       </c>
       <c r="K65" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N65" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L65" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O65" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>77</v>
@@ -8844,7 +8796,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -8856,7 +8808,7 @@
         <v>77</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>77</v>
@@ -8873,10 +8825,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8902,10 +8854,10 @@
         <v>107</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8932,13 +8884,13 @@
         <v>77</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>77</v>
@@ -8956,7 +8908,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>87</v>
@@ -8985,10 +8937,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9014,13 +8966,13 @@
         <v>101</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9070,7 +9022,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>87</v>
@@ -9099,10 +9051,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9125,17 +9077,15 @@
         <v>88</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>77</v>
@@ -9184,7 +9134,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9213,10 +9163,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9239,17 +9189,15 @@
         <v>88</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>77</v>
@@ -9298,7 +9246,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9327,10 +9275,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9353,17 +9301,15 @@
         <v>88</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="N70" s="2"/>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>77</v>
@@ -9412,7 +9358,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -9441,10 +9387,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9467,17 +9413,15 @@
         <v>88</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="N71" s="2"/>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>77</v>
@@ -9526,7 +9470,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -9555,10 +9499,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9581,13 +9525,13 @@
         <v>88</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -9638,7 +9582,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -9647,7 +9591,7 @@
         <v>87</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>99</v>
@@ -9656,7 +9600,7 @@
         <v>77</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>77</v>
@@ -9667,10 +9611,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9693,13 +9637,13 @@
         <v>77</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9750,7 +9694,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -9768,7 +9712,7 @@
         <v>77</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>77</v>
@@ -9779,14 +9723,14 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
@@ -9805,16 +9749,16 @@
         <v>77</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N74" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -9852,19 +9796,19 @@
         <v>77</v>
       </c>
       <c r="AB74" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC74" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE74" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -9876,13 +9820,13 @@
         <v>77</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>77</v>
@@ -9893,14 +9837,14 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -9919,19 +9863,19 @@
         <v>88</v>
       </c>
       <c r="K75" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N75" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L75" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O75" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>77</v>
@@ -9980,7 +9924,7 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -9992,7 +9936,7 @@
         <v>77</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>77</v>
@@ -10009,10 +9953,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10035,17 +9979,15 @@
         <v>88</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="N76" s="2"/>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>77</v>
@@ -10094,7 +10036,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>87</v>
@@ -10123,10 +10065,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10152,14 +10094,12 @@
         <v>101</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>182</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="N77" s="2"/>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>77</v>
@@ -10208,7 +10148,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -10237,10 +10177,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10263,16 +10203,16 @@
         <v>88</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -10322,7 +10262,7 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -10351,10 +10291,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10377,16 +10317,16 @@
         <v>88</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -10436,7 +10376,7 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -10465,10 +10405,10 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10491,16 +10431,16 @@
         <v>88</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -10550,7 +10490,7 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -10568,7 +10508,7 @@
         <v>77</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>205</v>
+        <v>77</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>77</v>
@@ -10579,13 +10519,13 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="D81" t="s" s="2">
         <v>77</v>
@@ -10607,13 +10547,13 @@
         <v>88</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -10664,7 +10604,7 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -10673,16 +10613,16 @@
         <v>79</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>120</v>
+        <v>77</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>77</v>
@@ -10693,10 +10633,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -10719,13 +10659,13 @@
         <v>77</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -10776,7 +10716,7 @@
         <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -10794,7 +10734,7 @@
         <v>77</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>77</v>
@@ -10805,14 +10745,14 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -10831,16 +10771,16 @@
         <v>77</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N83" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L83" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -10878,19 +10818,19 @@
         <v>77</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC83" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -10902,13 +10842,13 @@
         <v>77</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>77</v>
@@ -10919,14 +10859,14 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -10945,19 +10885,19 @@
         <v>88</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N84" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L84" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M84" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O84" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>77</v>
@@ -11006,7 +10946,7 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -11018,7 +10958,7 @@
         <v>77</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>77</v>
@@ -11035,10 +10975,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11064,10 +11004,10 @@
         <v>80</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11118,7 +11058,7 @@
         <v>77</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -11130,7 +11070,7 @@
         <v>77</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>77</v>
@@ -11147,10 +11087,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11176,13 +11116,13 @@
         <v>101</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -11232,7 +11172,7 @@
         <v>77</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -11261,10 +11201,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11287,16 +11227,16 @@
         <v>77</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -11346,7 +11286,7 @@
         <v>77</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -11364,7 +11304,7 @@
         <v>77</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>77</v>
@@ -11375,10 +11315,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11401,13 +11341,13 @@
         <v>88</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -11458,7 +11398,7 @@
         <v>77</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -11467,7 +11407,7 @@
         <v>87</v>
       </c>
       <c r="AI88" t="s" s="2">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="AJ88" t="s" s="2">
         <v>99</v>
@@ -11476,7 +11416,7 @@
         <v>77</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>77</v>
@@ -11487,10 +11427,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11513,13 +11453,13 @@
         <v>77</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -11570,7 +11510,7 @@
         <v>77</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -11588,7 +11528,7 @@
         <v>77</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>77</v>
@@ -11599,14 +11539,14 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -11625,16 +11565,16 @@
         <v>77</v>
       </c>
       <c r="K90" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N90" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L90" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -11672,19 +11612,19 @@
         <v>77</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC90" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD90" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -11696,13 +11636,13 @@
         <v>77</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK90" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>77</v>
@@ -11713,14 +11653,14 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -11739,19 +11679,19 @@
         <v>88</v>
       </c>
       <c r="K91" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N91" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L91" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M91" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O91" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>77</v>
@@ -11800,7 +11740,7 @@
         <v>77</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -11812,7 +11752,7 @@
         <v>77</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK91" t="s" s="2">
         <v>77</v>
@@ -11829,10 +11769,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -11858,13 +11798,13 @@
         <v>107</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -11890,13 +11830,13 @@
         <v>77</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>77</v>
@@ -11914,7 +11854,7 @@
         <v>77</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -11943,10 +11883,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -11969,16 +11909,16 @@
         <v>88</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -12028,7 +11968,7 @@
         <v>77</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -12037,7 +11977,7 @@
         <v>87</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>120</v>
+        <v>77</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>99</v>
@@ -12046,7 +11986,7 @@
         <v>77</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>77</v>
@@ -12057,10 +11997,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12083,13 +12023,13 @@
         <v>88</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" s="2"/>
@@ -12140,7 +12080,7 @@
         <v>77</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -12149,7 +12089,7 @@
         <v>87</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>99</v>
@@ -12158,7 +12098,7 @@
         <v>77</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>77</v>
@@ -12169,10 +12109,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12195,13 +12135,13 @@
         <v>77</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -12252,7 +12192,7 @@
         <v>77</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -12270,7 +12210,7 @@
         <v>77</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>77</v>
@@ -12281,14 +12221,14 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -12307,16 +12247,16 @@
         <v>77</v>
       </c>
       <c r="K96" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N96" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L96" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -12354,19 +12294,19 @@
         <v>77</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -12378,13 +12318,13 @@
         <v>77</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK96" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>77</v>
@@ -12395,14 +12335,14 @@
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -12421,19 +12361,19 @@
         <v>88</v>
       </c>
       <c r="K97" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N97" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L97" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O97" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>77</v>
@@ -12482,7 +12422,7 @@
         <v>77</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -12494,7 +12434,7 @@
         <v>77</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>77</v>
@@ -12511,10 +12451,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12540,10 +12480,10 @@
         <v>107</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -12570,13 +12510,13 @@
         <v>77</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>77</v>
@@ -12594,7 +12534,7 @@
         <v>77</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>87</v>
@@ -12623,10 +12563,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -12652,13 +12592,13 @@
         <v>101</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -12708,7 +12648,7 @@
         <v>77</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>87</v>
@@ -12737,10 +12677,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -12763,17 +12703,15 @@
         <v>88</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="N100" s="2"/>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>77</v>
@@ -12822,7 +12760,7 @@
         <v>77</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -12851,10 +12789,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -12877,17 +12815,15 @@
         <v>88</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>245</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="N101" s="2"/>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
         <v>77</v>
@@ -12936,7 +12872,7 @@
         <v>77</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -12965,10 +12901,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -12991,17 +12927,15 @@
         <v>88</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="N102" s="2"/>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
         <v>77</v>
@@ -13050,7 +12984,7 @@
         <v>77</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -13079,10 +13013,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13105,17 +13039,15 @@
         <v>88</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>241</v>
+      </c>
+      <c r="N103" s="2"/>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>77</v>
@@ -13164,7 +13096,7 @@
         <v>77</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -13193,10 +13125,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13219,13 +13151,13 @@
         <v>88</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -13276,7 +13208,7 @@
         <v>77</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -13285,7 +13217,7 @@
         <v>87</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>99</v>
@@ -13294,7 +13226,7 @@
         <v>77</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>77</v>
@@ -13305,10 +13237,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13331,13 +13263,13 @@
         <v>77</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -13388,7 +13320,7 @@
         <v>77</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -13406,7 +13338,7 @@
         <v>77</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>77</v>
@@ -13417,14 +13349,14 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
@@ -13443,16 +13375,16 @@
         <v>77</v>
       </c>
       <c r="K106" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N106" t="s" s="2">
         <v>160</v>
-      </c>
-      <c r="L106" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>163</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -13490,19 +13422,19 @@
         <v>77</v>
       </c>
       <c r="AB106" t="s" s="2">
-        <v>164</v>
+        <v>77</v>
       </c>
       <c r="AC106" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AD106" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE106" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -13514,13 +13446,13 @@
         <v>77</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>77</v>
@@ -13531,14 +13463,14 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
@@ -13557,19 +13489,19 @@
         <v>88</v>
       </c>
       <c r="K107" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="N107" t="s" s="2">
         <v>160</v>
       </c>
-      <c r="L107" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>163</v>
-      </c>
       <c r="O107" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>77</v>
@@ -13618,7 +13550,7 @@
         <v>77</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -13630,7 +13562,7 @@
         <v>77</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>77</v>
@@ -13647,10 +13579,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -13673,17 +13605,15 @@
         <v>88</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>178</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="N108" s="2"/>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
         <v>77</v>
@@ -13732,7 +13662,7 @@
         <v>77</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>87</v>
@@ -13761,10 +13691,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -13790,14 +13720,12 @@
         <v>101</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>182</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="N109" s="2"/>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
         <v>77</v>
@@ -13846,7 +13774,7 @@
         <v>77</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -13875,10 +13803,10 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -13901,16 +13829,16 @@
         <v>88</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -13960,7 +13888,7 @@
         <v>77</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -13989,10 +13917,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14015,16 +13943,16 @@
         <v>88</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -14074,7 +14002,7 @@
         <v>77</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -14103,10 +14031,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14129,16 +14057,16 @@
         <v>88</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -14188,7 +14116,7 @@
         <v>77</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -14206,7 +14134,7 @@
         <v>77</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>205</v>
+        <v>77</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>77</v>
@@ -14217,10 +14145,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14243,19 +14171,19 @@
         <v>88</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="O113" t="s" s="2">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>77</v>
@@ -14304,7 +14232,7 @@
         <v>77</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
@@ -14313,7 +14241,7 @@
         <v>87</v>
       </c>
       <c r="AI113" t="s" s="2">
-        <v>120</v>
+        <v>77</v>
       </c>
       <c r="AJ113" t="s" s="2">
         <v>99</v>
@@ -14322,7 +14250,7 @@
         <v>77</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>77</v>
